--- a/plantillas/Comunidad_PLANTILLA.xlsx
+++ b/plantillas/Comunidad_PLANTILLA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="611" firstSheet="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="611" firstSheet="6" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATOS" sheetId="1" state="visible" r:id="rId1"/>
@@ -1540,7 +1540,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1581,7 +1580,6 @@
       <c r="N5" s="7" t="n"/>
       <c r="R5" s="35" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="X7" s="35" t="n"/>
       <c r="Y7" s="35" t="n"/>
@@ -1749,7 +1747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="5.5703125" customWidth="1" style="1" min="1" max="1"/>
@@ -1817,8 +1815,6 @@
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="16.5" customFormat="1" customHeight="1" s="13">
       <c r="A8" s="216" t="n"/>
       <c r="B8" s="216" t="inlineStr">
@@ -2087,8 +2083,6 @@
       <c r="K5" s="7" t="n"/>
       <c r="P5" s="1" t="n"/>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="16.5" customFormat="1" customHeight="1" s="13">
       <c r="A8" s="216" t="n"/>
       <c r="B8" s="216" t="inlineStr">
@@ -2426,7 +2420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="53.42578125" customWidth="1" min="1" max="1"/>
@@ -2459,7 +2453,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="140" t="inlineStr">
         <is>
@@ -2548,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" style="1" min="1" max="1"/>
@@ -2722,7 +2715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15.7109375" customWidth="1" min="2" max="3"/>
@@ -2737,10 +2730,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CDAD. PROP. UN AMERICANO EN PARIS 59-71 Y OTROS</t>
-        </is>
+      <c r="A1" s="1">
+        <f>DATOS!A1</f>
+        <v/>
       </c>
     </row>
     <row r="2">
@@ -2768,7 +2760,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="16.5" customFormat="1" customHeight="1" s="13">
       <c r="A6" s="216" t="n"/>
       <c r="B6" s="216" t="inlineStr">
@@ -2861,7 +2852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S127"/>
+  <dimension ref="C2:S127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col width="3.28515625" customWidth="1" style="1" min="1" max="2"/>
@@ -2874,7 +2865,6 @@
     <col width="11.42578125" customWidth="1" style="1" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="15" customHeight="1">
       <c r="G2" s="240">
         <f>DATOS!A1</f>
@@ -2893,10 +2883,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1">
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -2941,8 +2927,9 @@
           <t>m3 CONSUMIDOS:</t>
         </is>
       </c>
-      <c r="G12" s="78" t="n">
-        <v>2704</v>
+      <c r="G12" s="78">
+        <f>'LECTURAS ACS M3'!G73</f>
+        <v/>
       </c>
       <c r="H12" s="79" t="inlineStr">
         <is>
@@ -3017,8 +3004,9 @@
           <t>kWh CONSUMIDOS:</t>
         </is>
       </c>
-      <c r="G17" s="78" t="n">
-        <v>89404</v>
+      <c r="G17" s="78">
+        <f>'LECTURAS CALEF KWH'!G82</f>
+        <v/>
       </c>
       <c r="H17" s="79" t="inlineStr">
         <is>
@@ -3084,8 +3072,9 @@
         <f>H24/H$31</f>
         <v/>
       </c>
-      <c r="H24" s="84" t="n">
-        <v>82090.49000000001</v>
+      <c r="H24" s="84">
+        <f>GAS!L98</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -3098,8 +3087,9 @@
         <f>H25/H$31</f>
         <v/>
       </c>
-      <c r="H25" s="84" t="n">
-        <v>8823.92</v>
+      <c r="H25" s="84">
+        <f>ELECTRICIDAD!H53</f>
+        <v/>
       </c>
       <c r="I25" s="76" t="n"/>
     </row>
@@ -3141,8 +3131,9 @@
         <f>H28/H$31</f>
         <v/>
       </c>
-      <c r="H28" s="84" t="n">
-        <v>3000</v>
+      <c r="H28" s="84">
+        <f>AGUA!V59</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -3155,8 +3146,9 @@
         <f>H29/H$31</f>
         <v/>
       </c>
-      <c r="H29" s="84" t="n">
-        <v>2673.81</v>
+      <c r="H29" s="84">
+        <f>AGUA!W59</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1">
@@ -3197,11 +3189,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37" ht="15" customHeight="1">
       <c r="E37" s="88" t="inlineStr">
         <is>
@@ -3393,9 +3380,6 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="15" customHeight="1">
       <c r="C48" s="176" t="inlineStr">
         <is>
@@ -3641,13 +3625,6 @@
         <v/>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
     <row r="64">
       <c r="C64" s="1" t="inlineStr">
         <is>
@@ -3679,7 +3656,6 @@
     <row r="68" ht="16.5" customHeight="1">
       <c r="C68" s="76" t="n"/>
     </row>
-    <row r="69"/>
     <row r="70" ht="15" customHeight="1">
       <c r="G70" s="241" t="n"/>
     </row>
@@ -3696,8 +3672,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
-    <row r="74"/>
     <row r="75" ht="15" customHeight="1">
       <c r="C75" s="117" t="inlineStr">
         <is>
@@ -3927,8 +3901,9 @@
         <v/>
       </c>
       <c r="I85" s="51" t="n"/>
-      <c r="J85" s="123" t="n">
-        <v>16224</v>
+      <c r="J85" s="123">
+        <f>'LECTURAS ACS M3'!H73</f>
+        <v/>
       </c>
       <c r="K85" s="56" t="n"/>
     </row>
@@ -3956,7 +3931,6 @@
       </c>
       <c r="K86" s="122" t="n"/>
     </row>
-    <row r="87"/>
     <row r="88" ht="15" customHeight="1">
       <c r="C88" s="106" t="n"/>
       <c r="D88" s="106" t="n"/>
@@ -4063,7 +4037,6 @@
     <row r="94">
       <c r="H94" s="67" t="n"/>
     </row>
-    <row r="95"/>
     <row r="96" ht="15" customHeight="1">
       <c r="C96" s="117" t="inlineStr">
         <is>
@@ -4282,8 +4255,9 @@
         <v/>
       </c>
       <c r="I106" s="51" t="n"/>
-      <c r="J106" s="123" t="n">
-        <v>17880.8</v>
+      <c r="J106" s="123">
+        <f>'LECTURAS CALEF KWH'!H82</f>
+        <v/>
       </c>
       <c r="K106" s="56" t="n"/>
     </row>
@@ -4311,7 +4285,6 @@
       </c>
       <c r="K107" s="122" t="n"/>
     </row>
-    <row r="108"/>
     <row r="109" ht="15" customHeight="1">
       <c r="C109" s="106" t="n"/>
       <c r="D109" s="106" t="n"/>
@@ -4352,7 +4325,7 @@
         <v/>
       </c>
       <c r="H110" s="137">
-        <f>-G110+8.5</f>
+        <f>-G110+F110</f>
         <v/>
       </c>
       <c r="I110" s="106" t="inlineStr">
@@ -4383,7 +4356,7 @@
         <v/>
       </c>
       <c r="H111" s="137">
-        <f>-G111+0.17</f>
+        <f>-G111+F111</f>
         <v/>
       </c>
       <c r="I111" s="106" t="inlineStr">
@@ -4404,13 +4377,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120" ht="15" customHeight="1" thickBot="1"/>
     <row r="121" ht="15" customHeight="1" thickTop="1">
       <c r="C121" s="132" t="n"/>
@@ -4559,7 +4525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A2:I102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="6.85546875" defaultRowHeight="14.25"/>
   <cols>
     <col width="3.28515625" customWidth="1" style="1" min="1" max="1"/>
@@ -4571,7 +4537,6 @@
     <col width="6.85546875" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="240">
         <f>DATOS!A1</f>
@@ -4591,9 +4556,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1">
       <c r="D8" s="160" t="inlineStr">
         <is>
@@ -4682,8 +4644,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="E16" s="29" t="n"/>
     </row>
@@ -4827,8 +4787,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="15" customHeight="1">
       <c r="B31" s="117" t="inlineStr">
         <is>
@@ -4994,15 +4952,6 @@
     <row r="50">
       <c r="E50" s="29" t="n"/>
     </row>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60" ht="15" customHeight="1">
       <c r="D60" s="160" t="inlineStr">
         <is>
@@ -5062,7 +5011,7 @@
     <row r="64">
       <c r="B64" s="103" t="inlineStr">
         <is>
-          <t>CUOTA FIJA MES ACS (€/mes):</t>
+          <t>CUOTA FIJA MES CALEFACCION (€/mes):</t>
         </is>
       </c>
       <c r="D64" s="168" t="inlineStr">
@@ -5078,7 +5027,7 @@
     <row r="65">
       <c r="B65" s="103" t="inlineStr">
         <is>
-          <t>PRECIO M3 (€/kWh):</t>
+          <t>PRECIO kWh (€/kWh):</t>
         </is>
       </c>
       <c r="D65" s="169" t="inlineStr">
@@ -5091,8 +5040,6 @@
         <v/>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67"/>
     <row r="68">
       <c r="E68" s="29" t="n"/>
     </row>
@@ -5117,7 +5064,7 @@
         </is>
       </c>
       <c r="E70" s="177">
-        <f>'ANALISIS PLANTILLA'!H24</f>
+        <f>'ANALISIS PLANTILLA'!G97</f>
         <v/>
       </c>
     </row>
@@ -5127,8 +5074,9 @@
           <t>ELECTRICIDAD</t>
         </is>
       </c>
-      <c r="E71" s="215" t="n">
-        <v>3562.68</v>
+      <c r="E71" s="215">
+        <f>'ANALISIS PLANTILLA'!G98</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -5138,7 +5086,7 @@
         </is>
       </c>
       <c r="E72" s="177">
-        <f>'ANALISIS PLANTILLA'!H26</f>
+        <f>'ANALISIS PLANTILLA'!G99</f>
         <v/>
       </c>
     </row>
@@ -5149,7 +5097,7 @@
         </is>
       </c>
       <c r="E73" s="177">
-        <f>'ANALISIS PLANTILLA'!H27</f>
+        <f>'ANALISIS PLANTILLA'!G100</f>
         <v/>
       </c>
     </row>
@@ -5160,7 +5108,7 @@
         </is>
       </c>
       <c r="E74" s="177">
-        <f>'ANALISIS PLANTILLA'!H28</f>
+        <f>'ANALISIS PLANTILLA'!G101</f>
         <v/>
       </c>
     </row>
@@ -5171,7 +5119,7 @@
         </is>
       </c>
       <c r="E75" s="177">
-        <f>'ANALISIS PLANTILLA'!H29</f>
+        <f>'ANALISIS PLANTILLA'!G102</f>
         <v/>
       </c>
     </row>
@@ -5182,7 +5130,7 @@
         </is>
       </c>
       <c r="E76" s="177">
-        <f>'ANALISIS PLANTILLA'!H30</f>
+        <f>'ANALISIS PLANTILLA'!G103</f>
         <v/>
       </c>
     </row>
@@ -5235,8 +5183,6 @@
         <v/>
       </c>
     </row>
-    <row r="81"/>
-    <row r="82"/>
     <row r="83" ht="15" customHeight="1">
       <c r="B83" s="117" t="inlineStr">
         <is>
@@ -5402,8 +5348,6 @@
     <row r="102">
       <c r="E102" s="29" t="n"/>
     </row>
-    <row r="103"/>
-    <row r="104"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:I4"/>
@@ -5637,13 +5581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D32E0F4-058C-4D3C-85FF-48A06AE475A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE26FCF-D35D-4E4F-A42A-DC2964CAF088}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B4FA0C5-3E12-4ECE-9A9E-FBF1AC8D7E6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F7753C-696F-49DC-A80C-B8DE7892E371}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD5129F-42F1-4636-BB4A-B198B40A89A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D551AB-718E-4CE3-84E7-42136D13EB7C}"/>
 </file>
--- a/plantillas/Comunidad_PLANTILLA.xlsx
+++ b/plantillas/Comunidad_PLANTILLA.xlsx
@@ -2420,7 +2420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="53.42578125" customWidth="1" min="1" max="1"/>
@@ -2487,17 +2487,37 @@
         </is>
       </c>
       <c r="B6" s="45" t="n"/>
-      <c r="F6" s="45" t="n">
-        <v>2847.16</v>
-      </c>
-      <c r="G6" s="45" t="n">
-        <v>2205.87</v>
-      </c>
-      <c r="H6" s="45" t="n">
-        <v>2387.1</v>
-      </c>
-      <c r="I6" s="45" t="n">
-        <v>2592.66</v>
+      <c r="F6" s="45" t="n"/>
+      <c r="G6" s="45" t="n"/>
+      <c r="H6" s="45" t="n"/>
+      <c r="I6" s="45" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LECTURAS CONTADORES CALEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PLACAS SOLARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO SALA CALDERAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO CORRECTIVO (REPARACIONES)</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1"/>
@@ -3104,7 +3124,7 @@
         <v/>
       </c>
       <c r="H26" s="84" t="n">
-        <v>4694.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3118,7 +3138,7 @@
         <v/>
       </c>
       <c r="H27" s="84" t="n">
-        <v>2684.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3164,7 +3184,7 @@
         <v/>
       </c>
       <c r="H30" s="85" t="n">
-        <v>3299.44</v>
+        <v>0</v>
       </c>
       <c r="I30" s="76" t="inlineStr">
         <is>
@@ -5581,13 +5601,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE26FCF-D35D-4E4F-A42A-DC2964CAF088}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25BFC64A-1714-47B1-BFF6-A733B4EC99FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F7753C-696F-49DC-A80C-B8DE7892E371}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9230A707-371D-47BA-AD0B-12C0398A2119}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D551AB-718E-4CE3-84E7-42136D13EB7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78AA1EAD-D483-414E-A883-2766BFFF943B}"/>
 </file>
--- a/plantillas/Comunidad_PLANTILLA.xlsx
+++ b/plantillas/Comunidad_PLANTILLA.xlsx
@@ -1450,7 +1450,7 @@
     <row r="1" ht="14.25" customFormat="1" customHeight="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CDAD. PROP. EL SEPTIMO SELLO 14-22 / EL TAMBOR DE HOJALATA 13-21</t>
+          <t>NOMBRE DE LA COMUNIDAD</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>EL SEPTIMO SELLO 18</t>
+          <t/>
         </is>
       </c>
       <c r="F4" s="22" t="n"/>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>ES0208330734612001PV</t>
+          <t/>
         </is>
       </c>
       <c r="F5" s="22" t="n"/>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>EL SEPTIMO SELLO 18, S.G.COM.</t>
+          <t/>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>ES0031300718351002PS0F</t>
+          <t/>
         </is>
       </c>
       <c r="F5" s="7" t="n"/>
@@ -2058,7 +2058,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ZARAGOZA + ECOCIUDAD VALDESPARTERA</t>
+          <t>SUMINISTRO DE AGUA</t>
         </is>
       </c>
     </row>
